--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.4%</t>
+          <t>-521.3%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.0%</t>
+          <t>-211.9%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45895,10 +45895,10 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.598570508392246</v>
+        <v>-3.59748496090761</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.642568401395953</v>
+        <v>1.643002620389807</v>
       </c>
       <c r="F1928" t="n">
         <v>0.03893512839987956</v>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.6%</t>
+          <t>498.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.3%</t>
+          <t>-545.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.9%</t>
+          <t>-221.7%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45895,10 +45895,10 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.59748496090761</v>
+        <v>-3.840903713177571</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.643002620389807</v>
+        <v>1.545635119481823</v>
       </c>
       <c r="F1928" t="n">
         <v>0.03893512839987956</v>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,65 +801,65 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-28.5%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.0%</t>
+          <t>498.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.5%</t>
+          <t>-163.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1928"/>
+  <dimension ref="A1:G1929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.509795375208456</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
@@ -45905,6 +45905,29 @@
       </c>
       <c r="G1928" t="n">
         <v>3.105714106106527</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="2" t="n">
+        <v>45391</v>
+      </c>
+      <c r="B1929" t="n">
+        <v>3.518474592671158</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>2.831288860699269</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>-3.840903713177571</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>1.545635119481823</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>0.03893512839987956</v>
+      </c>
+      <c r="G1929" t="n">
+        <v>2.824352657685637</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,75 +791,75 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-694.2%</t>
+          <t>-681.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-55.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.1%</t>
+          <t>502.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-545.7%</t>
+          <t>-533.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>-267.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.7%</t>
+          <t>-216.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-154.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.6%</t>
+          <t>-126.3%</t>
         </is>
       </c>
     </row>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923094</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795255984503029</v>
+        <v>-8.670804440587224</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053229678267694</v>
+        <v>-0.3555423502604471</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297756</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.17825737324566</v>
+        <v>-9.053805829329855</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5586256246454058</v>
+        <v>-0.5088450070790835</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.428791155501132</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6562676215761645</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.788321478005134</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.7947294472797148</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.11472150667015</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9173734387885424</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.23269690379239</v>
+        <v>-10.10824535987659</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9615218470156717</v>
+        <v>-0.9117412294493499</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.39284953692766</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22900597883598</v>
+        <v>-10.10455443492018</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9600454770331077</v>
+        <v>-0.9102648594667859</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.39284953692766</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.43326415416585</v>
+        <v>-10.30881261025004</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.036235550046411</v>
+        <v>-0.9864549324800889</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.520488481541649</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.59390318065421</v>
+        <v>-10.46945163673841</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.096008606157321</v>
+        <v>-1.046227988590999</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.635221954544045</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.52043334898676</v>
+        <v>-10.39598180507096</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.05124897199692</v>
+        <v>-1.001468354430598</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.561752122876596</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.69555776637331</v>
+        <v>-10.5711062224575</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.106743518204021</v>
+        <v>-1.056962900637698</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.73687654026314</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.93000986038779</v>
+        <v>-10.80555831647199</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.207743520711413</v>
+        <v>-1.15796290314509</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.73687654026314</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.21781370492503</v>
+        <v>-11.09336216100923</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.329537249300284</v>
+        <v>-1.279756631733962</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.024680384800378</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.44763815208886</v>
+        <v>-11.32318660817305</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.420351238327258</v>
+        <v>-1.370570620760936</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.187327921870539</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.67966707182512</v>
+        <v>-11.55521552790931</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.510469077592648</v>
+        <v>-1.460688460026326</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.249340619058962</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.62765155785631</v>
+        <v>-11.5032000139405</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.485672536318722</v>
+        <v>-1.435891918752399</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.249340619058962</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.76932339958043</v>
+        <v>-11.64487185566462</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.543816499907112</v>
+        <v>-1.494035882340789</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.249340619058962</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.8682301400397</v>
+        <v>-11.7437785961239</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.568325785925949</v>
+        <v>-1.518545168359628</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.348247359518238</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.6690780328026</v>
+        <v>-11.5446264888868</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.501716076677793</v>
+        <v>-1.451935459111471</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.182924833568424</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.44323288008319</v>
+        <v>-11.31878133616739</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.401798942553821</v>
+        <v>-1.352018324987497</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.140998157981261</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.1569580677605</v>
+        <v>-11.03250652384469</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.286149873068684</v>
+        <v>-1.236369255502361</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.140998157981261</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.20985335580479</v>
+        <v>-11.08540181188898</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.30467421412429</v>
+        <v>-1.254893596557968</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.136042811892815</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.92594462487604</v>
+        <v>-10.80149308096023</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.185377017514154</v>
+        <v>-1.135596399947832</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.136042811892815</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.67895737468309</v>
+        <v>-10.55450583076728</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.096319379830839</v>
+        <v>-1.046538762264516</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.889055561699863</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.41512050747902</v>
+        <v>-10.29066896356321</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.000668114262119</v>
+        <v>-0.9508874966957959</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.889055561699863</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.14787870661062</v>
+        <v>-10.02342716269481</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8956059544141328</v>
+        <v>-0.8458253368478101</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.889055561699863</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.872069543210133</v>
+        <v>-9.747617999294325</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7855826040273999</v>
+        <v>-0.7358019864610772</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.800036253421129</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.848116002234175</v>
+        <v>-9.723664458318368</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7753326814915233</v>
+        <v>-0.7255520639252002</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.776082712445171</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.584056063911378</v>
+        <v>-9.459604519995571</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6829690223241567</v>
+        <v>-0.633188404757834</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.512022774122376</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.876976440406541</v>
+        <v>-8.752524896490733</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4029242065825227</v>
+        <v>-0.3531435890161996</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.512022774122376</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.627335410420589</v>
+        <v>-8.502883866504781</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3027241707003006</v>
+        <v>-0.2529435531339774</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.262381744136424</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.372793511079513</v>
+        <v>-8.248341967163705</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2015405897431131</v>
+        <v>-0.1517599721767904</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.007839844795348</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.139312288849915</v>
+        <v>-8.014860744934108</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1002236720134215</v>
+        <v>-0.05044305444709885</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774358622565749</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.959603758706042</v>
+        <v>-7.835152214790235</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03123247026883202</v>
+        <v>0.0185481472974911</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.717187118403053</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.827328285075156</v>
+        <v>-7.702876741159349</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01704520593054992</v>
+        <v>0.06682582349687261</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.584911644772167</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.636728610402003</v>
+        <v>-7.512277066486196</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09610013648744742</v>
+        <v>0.1458807540537705</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394311970099014</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.387728811718422</v>
+        <v>-7.263277267802615</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2086063971845387</v>
+        <v>0.2583870147508613</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394311970099014</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.493318801491527</v>
+        <v>-7.36886725757572</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03839447167607801</v>
+        <v>0.08817508924240114</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499901959872118</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.512053703610124</v>
+        <v>-7.387602159694317</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07944485270572565</v>
+        <v>0.1292254702720488</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.499901959872118</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.235315528939312</v>
+        <v>-7.110863985023505</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1935191345600451</v>
+        <v>0.2432997521263682</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.318085298762192</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.108423122504242</v>
+        <v>-6.983971578588434</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2355621108805952</v>
+        <v>0.2853427284469179</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.191192892327122</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.920835614594315</v>
+        <v>-6.796384070678508</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3036365019494727</v>
+        <v>0.3534171195157954</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.191192892327122</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.678687221140457</v>
+        <v>-6.55423567722465</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.414958213712159</v>
+        <v>0.4647388312784817</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.191192892327122</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.615457849372109</v>
+        <v>-6.491006305456302</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.434782082878693</v>
+        <v>0.4845627004450161</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.191192892327122</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.428970156995103</v>
+        <v>-6.304518613079296</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5068752538400725</v>
+        <v>0.5566558714063952</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.004705199950116</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.407820958091659</v>
+        <v>-6.283369414175852</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5230359116387753</v>
+        <v>0.5728165292050984</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.9835560010466728</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.164055516108215</v>
+        <v>-6.039603972192408</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6163227967792038</v>
+        <v>0.6661034143455269</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.9835560010466728</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.900027448914955</v>
+        <v>-5.775575904999148</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7240583375765239</v>
+        <v>0.7738389551428471</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.7816906022307193</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.65017705496588</v>
+        <v>-5.525725511050073</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.816740570139856</v>
+        <v>0.8665211877061791</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.7816906022307193</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.346609565961901</v>
+        <v>-5.222158022046094</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9417666892620962</v>
+        <v>0.9915473068284193</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.7816906022307193</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.273129657109887</v>
+        <v>-5.14867811319408</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9844861588574556</v>
+        <v>1.034266776423778</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.7082106933787049</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.048096657441064</v>
+        <v>-4.923645113525257</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.073519836341282</v>
+        <v>1.123300453907605</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4831776937098821</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.833462279804658</v>
+        <v>-4.70901073588885</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.164068388450162</v>
+        <v>1.213849006016485</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.2685433160734753</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.566861922830306</v>
+        <v>-4.442410378914499</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.251902790023698</v>
+        <v>1.301683407590021</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.2685433160734753</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.326431426025446</v>
+        <v>-4.201979882109638</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.34981806537052</v>
+        <v>1.399598682936843</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.02811281926861497</v>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.083640618376</v>
+        <v>-3.959189074460193</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.450863702265118</v>
+        <v>1.500644319831441</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.02811281926861497</v>
@@ -45872,10 +45872,10 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.844035526768911</v>
+        <v>-3.719583982853103</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.547384322825294</v>
+        <v>1.597164940391617</v>
       </c>
       <c r="F1927" t="n">
         <v>0.03893512839987956</v>
@@ -45895,10 +45895,10 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.840903713177571</v>
+        <v>-3.716452169261764</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.545635119481823</v>
+        <v>1.595415737048146</v>
       </c>
       <c r="F1928" t="n">
         <v>0.03893512839987956</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.518474592671158</v>
+        <v>3.859738813755539</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.831288860699269</v>
+        <v>3.204111808378589</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.840903713177571</v>
+        <v>-3.716452169261764</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.545635119481823</v>
+        <v>1.595415737048146</v>
       </c>
       <c r="F1929" t="n">
         <v>0.03893512839987956</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.824352657685637</v>
+        <v>3.197175605364957</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.7%</t>
+          <t>-683.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-533.2%</t>
+          <t>-510.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-267.3%</t>
+          <t>-267.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-216.7%</t>
+          <t>-207.7%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923094</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.670804440587224</v>
+        <v>-8.686906930150034</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3555423502604471</v>
+        <v>-0.3619833460855713</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297756</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.053805829329855</v>
+        <v>-9.069908318892665</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5088450070790835</v>
+        <v>-0.5152860029042077</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.428791155501132</v>
+        <v>-9.444893645063942</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6562676215761645</v>
+        <v>-0.6627086174012882</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.788321478005134</v>
+        <v>-9.804423967567944</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7947294472797148</v>
+        <v>-0.801170443104839</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.11472150667015</v>
+        <v>-10.13082399623296</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9173734387885424</v>
+        <v>-0.9238144346136665</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.10824535987659</v>
+        <v>-10.1243478494394</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9117412294493499</v>
+        <v>-0.918182225274474</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.39284953692766</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.10455443492018</v>
+        <v>-10.12065692448299</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9102648594667859</v>
+        <v>-0.9167058552919092</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.39284953692766</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.30881261025004</v>
+        <v>-10.32491509981285</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9864549324800889</v>
+        <v>-0.992895928305213</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.520488481541649</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.46945163673841</v>
+        <v>-10.48555412630122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.046227988590999</v>
+        <v>-1.052668984416123</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.635221954544045</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.39598180507096</v>
+        <v>-10.41208429463377</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.001468354430598</v>
+        <v>-1.007909350255722</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.561752122876596</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.5711062224575</v>
+        <v>-10.58720871202031</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.056962900637698</v>
+        <v>-1.063403896462822</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.73687654026314</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.80555831647199</v>
+        <v>-10.8216608060348</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.15796290314509</v>
+        <v>-1.164403898970214</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.73687654026314</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.09336216100923</v>
+        <v>-11.10946465057204</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.279756631733962</v>
+        <v>-1.286197627559086</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.024680384800378</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.32318660817305</v>
+        <v>-11.33928909773586</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.370570620760936</v>
+        <v>-1.37701161658606</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.187327921870539</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.55521552790931</v>
+        <v>-11.57131801747212</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.460688460026326</v>
+        <v>-1.467129455851449</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.249340619058962</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.5032000139405</v>
+        <v>-11.51930250350331</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.435891918752399</v>
+        <v>-1.442332914577523</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.249340619058962</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.64487185566462</v>
+        <v>-11.66097434522743</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.494035882340789</v>
+        <v>-1.500476878165913</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.249340619058962</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.7437785961239</v>
+        <v>-11.75988108568671</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.518545168359628</v>
+        <v>-1.524986164184752</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.348247359518238</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.5446264888868</v>
+        <v>-11.56072897844961</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.451935459111471</v>
+        <v>-1.458376454936595</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.182924833568424</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.31878133616739</v>
+        <v>-11.3348838257302</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.352018324987497</v>
+        <v>-1.358459320812622</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.140998157981261</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.03250652384469</v>
+        <v>-11.0486090134075</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.236369255502361</v>
+        <v>-1.242810251327485</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.140998157981261</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.08540181188898</v>
+        <v>-11.10150430145179</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.254893596557968</v>
+        <v>-1.261334592383093</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.136042811892815</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.80149308096023</v>
+        <v>-10.81759557052304</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.135596399947832</v>
+        <v>-1.142037395772956</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.136042811892815</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.55450583076728</v>
+        <v>-10.57060832033009</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.046538762264516</v>
+        <v>-1.052979758089641</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.889055561699863</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.29066896356321</v>
+        <v>-10.30677145312602</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9508874966957959</v>
+        <v>-0.95732849252092</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.889055561699863</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.02342716269481</v>
+        <v>-10.03952965225762</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8458253368478101</v>
+        <v>-0.8522663326729352</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.889055561699863</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.747617999294325</v>
+        <v>-9.763720488857137</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7358019864610772</v>
+        <v>-0.7422429822862018</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.800036253421129</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.723664458318368</v>
+        <v>-9.739766947881179</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7255520639252002</v>
+        <v>-0.7319930597503252</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.776082712445171</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.459604519995571</v>
+        <v>-9.475707009558382</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.633188404757834</v>
+        <v>-0.6396294005829586</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.512022774122376</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.752524896490733</v>
+        <v>-8.768627386053545</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3531435890161996</v>
+        <v>-0.3595845848413246</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.512022774122376</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.502883866504781</v>
+        <v>-8.518986356067593</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2529435531339774</v>
+        <v>-0.2593845489591025</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.262381744136424</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.248341967163705</v>
+        <v>-8.264444456726517</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1517599721767904</v>
+        <v>-0.158200968001915</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.007839844795348</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.014860744934108</v>
+        <v>-8.03096323449692</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05044305444709885</v>
+        <v>-0.05688405027222343</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774358622565749</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.835152214790235</v>
+        <v>-7.851254704353047</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.0185481472974911</v>
+        <v>0.01210715147236652</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.717187118403053</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.702876741159349</v>
+        <v>-7.718979230722161</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.06682582349687261</v>
+        <v>0.06038482767174802</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.584911644772167</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.512277066486196</v>
+        <v>-7.528379556049008</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1458807540537705</v>
+        <v>0.1394397582286455</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394311970099014</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.263277267802615</v>
+        <v>-7.279379757365427</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2583870147508613</v>
+        <v>0.2519460189257368</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394311970099014</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.36886725757572</v>
+        <v>-7.384969747138531</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.08817508924240114</v>
+        <v>0.08173409341727655</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499901959872118</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.387602159694317</v>
+        <v>-7.403704649257128</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1292254702720488</v>
+        <v>0.1227844744469238</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.499901959872118</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.110863985023505</v>
+        <v>-7.126966474586316</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2432997521263682</v>
+        <v>0.2368587563012432</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.318085298762192</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.983971578588434</v>
+        <v>-7.000074068151246</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2853427284469179</v>
+        <v>0.2789017326217933</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.191192892327122</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.796384070678508</v>
+        <v>-6.81248656024132</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3534171195157954</v>
+        <v>0.3469761236906708</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.191192892327122</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.55423567722465</v>
+        <v>-6.570338166787462</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4647388312784817</v>
+        <v>0.4582978354533571</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.191192892327122</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.491006305456302</v>
+        <v>-6.507108795019113</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4845627004450161</v>
+        <v>0.4781217046198916</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.191192892327122</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.304518613079296</v>
+        <v>-6.320621102642107</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5566558714063952</v>
+        <v>0.5502148755812706</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.004705199950116</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.283369414175852</v>
+        <v>-6.299471903738664</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5728165292050984</v>
+        <v>0.5663755333799738</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.9835560010466728</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.039603972192408</v>
+        <v>-6.05570646175522</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6661034143455269</v>
+        <v>0.6596624185204019</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.9835560010466728</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.775575904999148</v>
+        <v>-5.791678394561959</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7738389551428471</v>
+        <v>0.7673979593177225</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.7816906022307193</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.525725511050073</v>
+        <v>-5.541828000612885</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8665211877061791</v>
+        <v>0.8600801918810541</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.7816906022307193</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.222158022046094</v>
+        <v>-5.238260511608906</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9915473068284193</v>
+        <v>0.9851063110032947</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.7816906022307193</v>
@@ -45734,10 +45734,10 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.14867811319408</v>
+        <v>-5.164780602756892</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.034266776423778</v>
+        <v>1.027825780598654</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.7082106933787049</v>
@@ -45757,10 +45757,10 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.923645113525257</v>
+        <v>-4.939747603088069</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.123300453907605</v>
+        <v>1.11685945808248</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4831776937098821</v>
@@ -45780,10 +45780,10 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.70901073588885</v>
+        <v>-4.725113225451662</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.213849006016485</v>
+        <v>1.20740801019136</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.2685433160734753</v>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.442410378914499</v>
+        <v>-4.45851286847731</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.301683407590021</v>
+        <v>1.295242411764896</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.2685433160734753</v>
@@ -45826,10 +45826,10 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.201979882109638</v>
+        <v>-4.21808237167245</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.399598682936843</v>
+        <v>1.393157687111718</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.02811281926861497</v>
@@ -45849,10 +45849,10 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.959189074460193</v>
+        <v>-3.975291564023005</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.500644319831441</v>
+        <v>1.494203324006316</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.02811281926861497</v>
@@ -45872,10 +45872,10 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.719583982853103</v>
+        <v>-3.735686472415915</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.597164940391617</v>
+        <v>1.590723944566492</v>
       </c>
       <c r="F1927" t="n">
         <v>0.03893512839987956</v>
@@ -45895,10 +45895,10 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.716452169261764</v>
+        <v>-3.493030883992752</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.595415737048146</v>
+        <v>1.684784251155751</v>
       </c>
       <c r="F1928" t="n">
         <v>0.03893512839987956</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.859738813755539</v>
+        <v>3.859738813755538</v>
       </c>
       <c r="C1929" t="n">
         <v>3.204111808378589</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.716452169261764</v>
+        <v>-3.493030883992752</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.595415737048146</v>
+        <v>1.684784251155751</v>
       </c>
       <c r="F1929" t="n">
         <v>0.03893512839987956</v>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923094</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297756</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.50317028234132</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309732</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858734</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.85615817609648</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180813</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.72996614056811</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963422</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.82854791119282</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262051</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389913</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788098</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749188</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481501</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.78093033586299</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102786</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.76461430435308</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544788</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.7976913087123</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837691</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349973</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972347</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.859738813755538</v>
+        <v>3.859738813755541</v>
       </c>
       <c r="C1929" t="n">
         <v>3.204111808378589</v>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.9%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-510.9%</t>
+          <t>-521.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-207.7%</t>
+          <t>-211.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.2%</t>
+          <t>-158.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.1%</t>
+          <t>-222.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.3%</t>
+          <t>-136.5%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234132</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776683</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69156815841072</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67683797424058</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085282</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282104</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116219</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081571</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425332</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702416</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781952</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567248</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487778</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309732</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858734</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609648</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761812</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575957</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430991</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077649</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457907</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180813</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879206</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996614056811</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963422</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119282</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262051</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389913</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788098</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749188</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481501</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093033586299</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102786</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435308</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544788</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976913087123</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837691</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349973</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972347</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.859738813755541</v>
+        <v>3.859738813755539</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.204111808378589</v>
+        <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.493030883992752</v>
+        <v>-3.594621751858893</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.684784251155751</v>
+        <v>1.645726941019908</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.03893512839987956</v>
+        <v>0.01844054730435396</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.197175605364957</v>
+        <v>3.094996394459826</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240409.xlsx
+++ b/tame_output/ON/bt/strategyON_20240409.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.4%</t>
+          <t>499.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.0%</t>
+          <t>-509.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.6%</t>
+          <t>-194.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.1%</t>
+          <t>-225.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-136.5%</t>
+          <t>-126.7%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.50317028234132</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.728574354425332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309732</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858734</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.518986356067593</v>
+        <v>-8.717386181315261</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2593845489591025</v>
+        <v>-0.3387444790581693</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.262381744136424</v>
+        <v>-2.460781569384091</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.791137371299828</v>
+        <v>1.672097476151228</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.85615817609648</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.264444456726517</v>
+        <v>-8.462844281974185</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.158200968001915</v>
+        <v>-0.2375608981009822</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.007839844795348</v>
+        <v>-2.206239670043015</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.943229332125231</v>
+        <v>1.82418943697663</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.03096323449692</v>
+        <v>-8.229363059744585</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05688405027222343</v>
+        <v>-0.1362439803712898</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.774358622565749</v>
+        <v>-1.972758447813417</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.091242494300842</v>
+        <v>1.972202599152242</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.851254704353047</v>
+        <v>-8.049654529600712</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.01210715147236652</v>
+        <v>-0.06725277862669987</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.717187118403053</v>
+        <v>-1.915586943650721</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.1226531864855</v>
+        <v>2.0036132913369</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.718979230722161</v>
+        <v>-7.917379055969826</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.06038482767174802</v>
+        <v>-0.01897510242731792</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.584911644772167</v>
+        <v>-1.783311470019834</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.19738595741106</v>
+        <v>2.078346062262459</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.528379556049008</v>
+        <v>-7.726779381296673</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1394397582286455</v>
+        <v>0.06007982812957957</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394311970099014</v>
+        <v>-1.592711795346681</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.314560822902588</v>
+        <v>2.195520927753988</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.279379757365427</v>
+        <v>-7.477779582613092</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2519460189257368</v>
+        <v>0.1725860888266708</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394311970099014</v>
+        <v>-1.592711795346681</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.327467164126247</v>
+        <v>2.208427268977647</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.384969747138531</v>
+        <v>-7.583369572386196</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.08173409341727655</v>
+        <v>0.002374163318210165</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499901959872118</v>
+        <v>-1.698301785119785</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.136137240663166</v>
+        <v>2.017097345514565</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.403704649257128</v>
+        <v>-7.602104474504793</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1227844744469238</v>
+        <v>0.04342454434785781</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.499901959872118</v>
+        <v>-1.698301785119785</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184681582540252</v>
+        <v>2.065641687391651</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180813</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.126966474586316</v>
+        <v>-7.325366299833981</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2368587563012432</v>
+        <v>0.1574988262021777</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.318085298762192</v>
+        <v>-1.51648512400986</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.297150591192202</v>
+        <v>2.178110696043602</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.000074068151246</v>
+        <v>-7.19847389339891</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2789017326217933</v>
+        <v>0.1995418025227278</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.191192892327122</v>
+        <v>-1.38959271757479</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.364572048799766</v>
+        <v>2.245532153651165</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.72996614056811</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.81248656024132</v>
+        <v>-7.010886385488984</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3469761236906708</v>
+        <v>0.2676161935916048</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.191192892327122</v>
+        <v>-1.38959271757479</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.357611436704673</v>
+        <v>2.238571541556072</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963422</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.570338166787462</v>
+        <v>-6.768737992035126</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4582978354533571</v>
+        <v>0.3789379053542912</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.191192892327122</v>
+        <v>-1.38959271757479</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.372073791085816</v>
+        <v>2.253033895937215</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.82854791119282</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.507108795019113</v>
+        <v>-6.705508620266778</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4781217046198916</v>
+        <v>0.3987617745208256</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.191192892327122</v>
+        <v>-1.38959271757479</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.366605911545011</v>
+        <v>2.24756601639641</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262051</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.320621102642107</v>
+        <v>-6.519020927889771</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5502148755812706</v>
+        <v>0.4708549454822051</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.004705199950116</v>
+        <v>-1.203105025197784</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.475996620981792</v>
+        <v>2.356956725833191</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389913</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.299471903738664</v>
+        <v>-6.497871728986328</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5663755333799738</v>
+        <v>0.4870156032809079</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.9835560010466728</v>
+        <v>-1.18195582629434</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.496387118561183</v>
+        <v>2.377347223412583</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788098</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.05570646175522</v>
+        <v>-6.254106287002884</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6596624185204019</v>
+        <v>0.5803024884213364</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.9835560010466728</v>
+        <v>-1.18195582629434</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.492167826908234</v>
+        <v>2.373127931759633</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.791678394561959</v>
+        <v>-5.990078219809623</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7673979593177225</v>
+        <v>0.6880380292186565</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.7816906022307193</v>
+        <v>-0.9800904274783866</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.615411380117822</v>
+        <v>2.496371484969222</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749188</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.541828000612885</v>
+        <v>-5.740227825860549</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8600801918810541</v>
+        <v>0.7807202617819886</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.7816906022307193</v>
+        <v>-0.9800904274783866</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.608153455101524</v>
+        <v>2.489113559952924</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481501</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.238260511608906</v>
+        <v>-5.43666033685657</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9851063110032947</v>
+        <v>0.9057463809042288</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.7816906022307193</v>
+        <v>-0.9800904274783866</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.611752578622173</v>
+        <v>2.492712683473572</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.78093033586299</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.164780602756892</v>
+        <v>-5.363180428004556</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.027825780598654</v>
+        <v>0.9484658504995882</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.7082106933787049</v>
+        <v>-0.9066105186263722</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.669168029987935</v>
+        <v>2.550128134839335</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102786</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.939747603088069</v>
+        <v>-5.138147428335733</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.11685945808248</v>
+        <v>1.037499527983414</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4831776937098821</v>
+        <v>-0.6815775189575494</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.803208307405526</v>
+        <v>2.684168412256926</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.76461430435308</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.725113225451662</v>
+        <v>-4.923513050699326</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.20740801019136</v>
+        <v>1.128048080092294</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.2685433160734753</v>
+        <v>-0.4669431413211426</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.936683735041687</v>
+        <v>2.817643839893087</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544788</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.45851286847731</v>
+        <v>-4.656912693724975</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.295242411764896</v>
+        <v>1.215882481665831</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.2685433160734753</v>
+        <v>-0.4669431413211426</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.917877993825483</v>
+        <v>2.798838098676883</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.7976913087123</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.21808237167245</v>
+        <v>-4.416482196920114</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.393157687111718</v>
+        <v>1.313797757012652</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.02811281926861497</v>
+        <v>-0.2265126445162823</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.063879368533276</v>
+        <v>2.944839473384676</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837691</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-3.975291564023005</v>
+        <v>-4.173691389270669</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.494203324006316</v>
+        <v>1.41484339390725</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.02811281926861497</v>
+        <v>-0.2265126445162823</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.067808682368097</v>
+        <v>2.948768787219496</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349973</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.735686472415915</v>
+        <v>-3.934086297663579</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.590723944566492</v>
+        <v>1.511364014467426</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.03893512839987956</v>
+        <v>-0.1594646968477877</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.108716034886533</v>
+        <v>2.989676139737933</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972347</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.493030883992752</v>
+        <v>-3.691430709240416</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.684784251155751</v>
+        <v>1.605424321056685</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.03893512839987956</v>
+        <v>-0.1594646968477877</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.105714106106527</v>
+        <v>2.986674210957927</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.859738813755539</v>
+        <v>3.548862472309235</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083932066077213</v>
+        <v>3.204111808378589</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.594621751858893</v>
+        <v>-3.476370781992078</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.645726941019908</v>
+        <v>1.81320707126801</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.01844054730435396</v>
+        <v>-0.01892530370036538</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.094996394459826</v>
+        <v>3.19275662615837</v>
       </c>
     </row>
   </sheetData>
